--- a/Result/checksun_type/銅箔.xlsx
+++ b/Result/checksun_type/銅箔.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>230.7</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>230.08</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>227.19</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>230.08</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>227.19</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1283102.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>10964527.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>10964527.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5735303.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7985358.06</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7985358.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>1051803.848784661</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1283102</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1283102.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>230.3</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>230.52</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>227.79</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>230.52</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>227.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>10278702.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>10837362.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>10837362.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5726125.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>8327959.58</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>8327959.58</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>1815315.448596958</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>10278702</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>10278702.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>228.3</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>230.35</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>228.45</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>230.35</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>228.45</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>19711075.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>8901343.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>8901343.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>4745840.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>8581109.76</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>8581109.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>1877399.325164635</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>19711075</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>19711075.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>227.6</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>229.55</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>228.88</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>229.55</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>228.88</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>16012123.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>5040826.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>5040826.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2836717.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>8534880.14</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>8534880.140000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>888429.2086482942</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>16012123</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>16012123.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>226.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>228.35</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>228.87</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>228.35</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>228.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>7537636.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1897152.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1897152.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1330188.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8598630.36</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8598630.359999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-159798.5723982039</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>7537636</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>7537636.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>225.1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>227.22</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>228.65</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>227.22</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>228.65</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>647277.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>506079.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>506079.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>643135.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8741054.44</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8741054.439999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-743578.9891646946</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>647277</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>647277.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>229.3</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>227.2</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>228.45</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>228.45</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>598606.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>614888.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>614888</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1598463.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>9009094.84</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>9009094.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-812741.8706466558</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>598606</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>598606.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>230.4</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>227.28</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>228.31</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>227.28</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>228.31</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>408491.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>590336.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>590336.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1824692.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>9613871.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>9613871.359999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-877304.7416692199</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>408491</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>408491.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>229.9</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>226.15</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>228.01</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>226.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>228.01</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>293752.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>632608.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>632608.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2121842.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>9986322.78</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>9986322.779999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-917835.6380704106</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>293752</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>293752.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>228.7</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>225.48</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>227.41</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>225.48</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>227.41</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>582273.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>763225.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>763225</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2276869.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>10041804.14</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>10041804.14</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-930663.6101410254</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>582273</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>582273.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>227.5</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>224.42</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>227.1</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>224.42</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>227.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1191318.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>780190.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>780190.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2309609.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>10073239.66</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>10073239.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-946664.2627368676</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1191318</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1191318.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>41.4</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>43.49</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>36.32</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>36.32</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>682461548.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>890512687.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>890512687.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>964944704.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>725273991.66</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>725273991.66</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-60004473.81528199</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>682461548</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>682461548.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>41.67999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>43.7</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>36.11</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>36.11</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>890768695.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>883596135.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>883596135.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1287123896.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>718113714.48</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>718113714.48</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-34854103.29192591</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>890768695</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>890768695.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>42.02</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>43.59</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>35.9</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1395221125.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>843818106.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>843818106.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1334451287.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>704499847.96</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>704499847.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-19998836.03384829</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1395221125</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1395221125.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>43.0</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>43.35</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>35.67</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>772163627.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>843889303.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>843889303.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1287691933.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>682634215.26</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>682634215.26</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-52111256.16395724</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>772163627</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>772163627.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>44.12</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>42.91</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>35.46</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>35.46</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>711948441.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>836814535.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>836814535</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1528157491.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>679161442.92</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>679161442.92</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-29368865.27254272</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>711948441</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>711948441.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>45.36</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>42.43</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>35.22</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>35.22</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>647878791.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1039376722.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1039376722.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1579097130.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>668897836.04</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>668897836.04</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>10620779.68921161</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>647878791</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>647878791.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>47.27</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>42.18</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>35</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>691878549.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1690651656.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1690651656.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1624661312.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>664039729.96</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>664039729.96</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>74234135.717103</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>691878549</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>691878549.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>48.4</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.88</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>34.74</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>34.74</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1395577108.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1825084468.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1825084468</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1654064683.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>657570889.42</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>657570889.42</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>157744879.6956229</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1395577108</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1395577108.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>47.81999999999999</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.27</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>34.44</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>34.44</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>736789786.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1731494563.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1731494563.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1555480127.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>641529240.7</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>641529240.7</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>196015922.6400931</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>736789786</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>736789786.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>47.11</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>40.64</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>34.15</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>34.15</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1724759379.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2219500447.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2219500447.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1581685303.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>628056168.02</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>628056168.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>314272628.3950469</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1724759379</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1724759379.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>46.57</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>40.02</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>33.81</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>3904253460.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2118817538.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2118817538.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1619529875.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>596756298.98</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>596756298.98</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>366132872.0665867</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>3904253460</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3904253460.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1408.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1390.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1390</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1874.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2505.32</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2505.32</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-162.3915940610709</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1408</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1408.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>897.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1319.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1319.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2147.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2523.66</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2523.66</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-161.590655999162</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>897</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>897.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>61.77</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2127.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1720.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1720</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>2206.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2581.7</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2581.7</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-99.92536391075078</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2127</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2127.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>61.72000000000001</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>61.82</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>62.15</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>62.15</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1337.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>1696.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>1696</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>2141.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2592.12</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2592.12</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-140.0490407876364</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1337</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1337.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>61.88</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>61.86</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>62.18</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>62.18</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1181.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1820.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1820</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>2048.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2632.5</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2632.5</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-107.7239705836289</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1181</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1181.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>61.91</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>62.19</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>62.19</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1057.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>2359.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>2359.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>2006.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2638.44</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2638.44</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-40.98372848563167</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1057</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1057.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>61.98</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>61.94</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>2898.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>2974.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>2974.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>2218.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2658.94</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2658.94</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>69.10889338599463</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>2898</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>2898.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>61.98</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>61.98</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>62.21</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>2007.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>2693.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>2693.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>2055.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2633.78</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2633.78</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>26.66589272453211</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>2007</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>2007.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>61.8</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>61.99</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1957.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>2586.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>2586.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1968.1</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2647.68</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2647.68</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>60.54496703942414</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1957</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1957.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>61.7</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>62.03</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>3877.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2276.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2276.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1891.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2631.9</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2631.9</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>112.1384672378617</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>3877</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>3877.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>61.6</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>62.08</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>62.21</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>4134.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1653.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1653.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1674.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2583.16</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2583.16</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-23.8757634514368</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>4134</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>4134.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>53.48</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>3512622548.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>6095469315.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>6095469315</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>9544851503.2</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>3663541757.9</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>3663541757.9</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>98808707.88450241</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>3512622548</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>3512622548.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>43.41</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>6744255965.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>6936487304.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>6936487304.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>10032139013.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>3632131847.42</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>3632131847.42</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>468208784.7071676</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>6744255965</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>6744255965.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>47.74</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>4850127005.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>8366597065.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>8366597065.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>9915210649.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>3525171118.12</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>3525171118.12</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>632955000.321434</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>4850127005</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>4850127005.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>4661687858.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>9917900867.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>9917900867.799999</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>9646311981.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>3483979320.62</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>3483979320.62</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>1048643589.758906</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>4661687858</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>4661687858.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>46.69</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>10708653199.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>11555043688.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>11555043688.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>9440522375.4</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>3413291777.02</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>3413291777.02</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>1625222783.642477</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>10708653199</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>10708653199.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>55.4</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>42.16</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>7717712495.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>12994233691.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>12994233691.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>8470087592.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>3233128694.92</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>3233128694.92</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>1742974531.810349</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>7717712495</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>7717712495.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>54.6</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>41.86</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>41.86</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>13894804772.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>13127790722.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>13127790722.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>7823899971.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>3109382048.22</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>3109382048.22</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>2169400157.056937</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>13894804772</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>13894804772.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>12606646015.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>11463824233.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>11463824233.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>6558502593.2</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2879764455.78</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2879764455.78</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>2039269729.264316</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>12606646015</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>12606646015.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>12847401961.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>9374723094.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>9374723094.799999</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>5390815186.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2722439698.1</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2722439698.1</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>1918555066.051131</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>12847401961</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>12847401961.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>17904603214.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>7326001062.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>7326001062.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>4299803431.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2525457286.94</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2525457286.94</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>1651790443.45904</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>17904603214</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>17904603214.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>44.51000000000001</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>40.69</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>8385497650.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3945941494.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>3945941494.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>2599113437.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2229827006.08</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2229827006.08</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>669862618.2396603</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>8385497650</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>8385497650.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
